--- a/data/team_stat.xlsx
+++ b/data/team_stat.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a225a4cd7e80232/Wasawat/Etheria/gvgplaner/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="112" documentId="11_625D4987526768CFEB3B98154B5DCE3A47CD54D3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B3B2437D-E63D-446A-8D26-FE216124473A}"/>
+  <xr:revisionPtr revIDLastSave="139" documentId="11_625D4987526768CFEB3B98154B5DCE3A47CD54D3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ECBE033C-D7C6-4F62-A9FA-3F61E3B3BD92}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="348" yWindow="1056" windowWidth="5424" windowHeight="10524" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Animus" sheetId="1" r:id="rId1"/>
-    <sheet name="W011" sheetId="3" r:id="rId2"/>
+    <sheet name="W010" sheetId="4" r:id="rId2"/>
+    <sheet name="W011" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -836,7 +837,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="85">
   <si>
     <t>Animus</t>
   </si>
@@ -2610,6 +2611,140 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0315EFF-635F-40C4-92EA-37C42B4E2E93}">
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" t="s">
+        <v>79</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>68</v>
+      </c>
+      <c r="B8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{6537F7E5-878A-4B64-B8FC-8BEECBC5A566}">
+          <x14:formula1>
+            <xm:f>Animus!$A$2:$A$80</xm:f>
+          </x14:formula1>
+          <xm:sqref>A2:C8</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEF9D56E-CE94-4D93-A8B5-535A0820AD51}">
   <dimension ref="A1:D15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/data/team_stat.xlsx
+++ b/data/team_stat.xlsx
@@ -8,14 +8,54 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a225a4cd7e80232/Wasawat/Etheria/gvgplaner/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="139" documentId="11_625D4987526768CFEB3B98154B5DCE3A47CD54D3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ECBE033C-D7C6-4F62-A9FA-3F61E3B3BD92}"/>
+  <xr:revisionPtr revIDLastSave="249" documentId="11_625D4987526768CFEB3B98154B5DCE3A47CD54D3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6DF04597-B833-4165-984E-849F32F31232}"/>
   <bookViews>
-    <workbookView xWindow="348" yWindow="1056" windowWidth="5424" windowHeight="10524" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="42" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Animus" sheetId="1" r:id="rId1"/>
     <sheet name="W010" sheetId="4" r:id="rId2"/>
     <sheet name="W011" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId4"/>
+    <sheet name="Sheet2" sheetId="6" r:id="rId5"/>
+    <sheet name="Sheet3" sheetId="7" r:id="rId6"/>
+    <sheet name="Sheet4" sheetId="8" r:id="rId7"/>
+    <sheet name="Sheet5" sheetId="9" r:id="rId8"/>
+    <sheet name="Sheet6" sheetId="10" r:id="rId9"/>
+    <sheet name="Sheet7" sheetId="11" r:id="rId10"/>
+    <sheet name="Sheet8" sheetId="12" r:id="rId11"/>
+    <sheet name="Sheet9" sheetId="13" r:id="rId12"/>
+    <sheet name="Sheet10" sheetId="14" r:id="rId13"/>
+    <sheet name="Sheet11" sheetId="15" r:id="rId14"/>
+    <sheet name="Sheet12" sheetId="16" r:id="rId15"/>
+    <sheet name="Sheet13" sheetId="17" r:id="rId16"/>
+    <sheet name="Sheet14" sheetId="18" r:id="rId17"/>
+    <sheet name="Sheet15" sheetId="19" r:id="rId18"/>
+    <sheet name="Sheet16" sheetId="20" r:id="rId19"/>
+    <sheet name="Sheet17" sheetId="21" r:id="rId20"/>
+    <sheet name="Sheet18" sheetId="22" r:id="rId21"/>
+    <sheet name="Sheet19" sheetId="23" r:id="rId22"/>
+    <sheet name="Sheet20" sheetId="24" r:id="rId23"/>
+    <sheet name="Sheet21" sheetId="25" r:id="rId24"/>
+    <sheet name="Sheet22" sheetId="26" r:id="rId25"/>
+    <sheet name="Sheet23" sheetId="27" r:id="rId26"/>
+    <sheet name="Sheet24" sheetId="28" r:id="rId27"/>
+    <sheet name="Sheet25" sheetId="29" r:id="rId28"/>
+    <sheet name="Sheet26" sheetId="30" r:id="rId29"/>
+    <sheet name="Sheet27" sheetId="31" r:id="rId30"/>
+    <sheet name="Sheet28" sheetId="32" r:id="rId31"/>
+    <sheet name="Sheet29" sheetId="33" r:id="rId32"/>
+    <sheet name="Sheet30" sheetId="34" r:id="rId33"/>
+    <sheet name="Sheet31" sheetId="35" r:id="rId34"/>
+    <sheet name="Sheet32" sheetId="36" r:id="rId35"/>
+    <sheet name="Sheet33" sheetId="37" r:id="rId36"/>
+    <sheet name="Sheet34" sheetId="38" r:id="rId37"/>
+    <sheet name="Sheet35" sheetId="39" r:id="rId38"/>
+    <sheet name="Sheet36" sheetId="40" r:id="rId39"/>
+    <sheet name="Sheet37" sheetId="41" r:id="rId40"/>
+    <sheet name="Sheet38" sheetId="42" r:id="rId41"/>
+    <sheet name="Sheet39" sheetId="43" r:id="rId42"/>
+    <sheet name="Sheet40" sheetId="44" r:id="rId43"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -2610,6 +2650,96 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E94464D4-EC1D-4FA0-AC40-66A467EC0964}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3AE0CA9-405C-4086-9C56-CE63580B449A}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15995D1D-FDF0-49C6-8ECD-4F5FC78221C7}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46922D0C-AA70-47C0-981A-967EE03D6C3C}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4D4A80C-4094-4F69-8614-637DB0E47D94}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62CFDE25-B95E-4367-88F9-4F9BFB49C1A6}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1B86F54-2294-49B8-ADD6-8EBAFCD85527}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53ECA507-449C-4C8A-A2AA-22A6B59F45D7}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89023118-6C73-4124-B7AA-225A3D06B710}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61575C6C-A079-42DD-B080-70791D352578}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0315EFF-635F-40C4-92EA-37C42B4E2E93}">
   <dimension ref="A1:D8"/>
@@ -2744,6 +2874,96 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51391442-8772-4747-A4BF-B475C7E33B1C}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2C0C972-BDE0-4FF5-9CBF-9CA51BBBEC53}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{224B232A-57F3-4811-86C9-FA17548A7E22}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28D69BCE-72F0-4D88-997B-5DB235E78B77}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C80B07B4-8CB3-415A-ABE2-3D5572F06803}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4FEC5A-A300-4B9A-A1C9-22BC0D6D8CB2}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ECD49C4-9D60-4B84-9C75-35D09029E2E6}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6367E4F9-1F1D-4D4C-A55B-2A720E92992F}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3745DC1-208B-48D0-AE15-C26A009618DC}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D51E4C66-F459-4454-AD60-333A1024BAB4}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEF9D56E-CE94-4D93-A8B5-535A0820AD51}">
   <dimension ref="A1:D15"/>
@@ -2974,4 +3194,184 @@
     </ext>
   </extLst>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FC1D91F-A606-4E23-BCC8-9DF35147A8FC}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3128FFCD-CB1D-4689-9AEA-B980E4E8AF28}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62335473-716F-41E1-B969-A29BAB24CE88}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B151F5B6-61D9-4E4D-A833-0A4E42510874}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C948862A-A018-4152-9AA1-E137DA89948C}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AE5714A-EE07-4ABB-B5B2-3ADBE3214464}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D358B63E-AC30-4B8E-AFA7-148098837145}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF1BFD0A-F4D1-48EB-A255-71E20A598CF1}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{663B8461-B94F-40E4-ABFF-F2A5B0C697EF}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF714D8E-0CDD-4814-8286-A3DBDC65584C}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA3FACD9-1807-42BF-B67D-498F268AAADA}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFABD89E-BB0B-4FD2-A11A-777F0F59CB49}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22005587-4C80-485E-B637-6D2394DE3CAE}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FBA76BF-0954-4E61-A150-B0A3899BA710}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40A39B4A-8FD5-4236-8396-62C97FF8DB07}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6019E687-BCD8-4FB3-9692-FA714D1CC31B}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E8BCAE6-FB71-4B36-9B23-91FA349B8AF1}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00CB4B69-3746-4982-A1F1-65B2ED3EFD11}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01DC096B-7A7C-40C0-9897-7CD7CA520658}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{616ED733-6DEB-463F-8060-428CB1F0EE76}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/team_stat.xlsx
+++ b/data/team_stat.xlsx
@@ -8,54 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a225a4cd7e80232/Wasawat/Etheria/gvgplaner/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="249" documentId="11_625D4987526768CFEB3B98154B5DCE3A47CD54D3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6DF04597-B833-4165-984E-849F32F31232}"/>
+  <xr:revisionPtr revIDLastSave="289" documentId="11_625D4987526768CFEB3B98154B5DCE3A47CD54D3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8B1D5AA-F7A7-43C4-89E6-0AC8023A0E64}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="42" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Animus" sheetId="1" r:id="rId1"/>
     <sheet name="W010" sheetId="4" r:id="rId2"/>
     <sheet name="W011" sheetId="3" r:id="rId3"/>
-    <sheet name="Sheet1" sheetId="5" r:id="rId4"/>
-    <sheet name="Sheet2" sheetId="6" r:id="rId5"/>
-    <sheet name="Sheet3" sheetId="7" r:id="rId6"/>
-    <sheet name="Sheet4" sheetId="8" r:id="rId7"/>
-    <sheet name="Sheet5" sheetId="9" r:id="rId8"/>
-    <sheet name="Sheet6" sheetId="10" r:id="rId9"/>
-    <sheet name="Sheet7" sheetId="11" r:id="rId10"/>
-    <sheet name="Sheet8" sheetId="12" r:id="rId11"/>
-    <sheet name="Sheet9" sheetId="13" r:id="rId12"/>
-    <sheet name="Sheet10" sheetId="14" r:id="rId13"/>
-    <sheet name="Sheet11" sheetId="15" r:id="rId14"/>
-    <sheet name="Sheet12" sheetId="16" r:id="rId15"/>
-    <sheet name="Sheet13" sheetId="17" r:id="rId16"/>
-    <sheet name="Sheet14" sheetId="18" r:id="rId17"/>
-    <sheet name="Sheet15" sheetId="19" r:id="rId18"/>
-    <sheet name="Sheet16" sheetId="20" r:id="rId19"/>
-    <sheet name="Sheet17" sheetId="21" r:id="rId20"/>
-    <sheet name="Sheet18" sheetId="22" r:id="rId21"/>
-    <sheet name="Sheet19" sheetId="23" r:id="rId22"/>
-    <sheet name="Sheet20" sheetId="24" r:id="rId23"/>
-    <sheet name="Sheet21" sheetId="25" r:id="rId24"/>
-    <sheet name="Sheet22" sheetId="26" r:id="rId25"/>
-    <sheet name="Sheet23" sheetId="27" r:id="rId26"/>
-    <sheet name="Sheet24" sheetId="28" r:id="rId27"/>
-    <sheet name="Sheet25" sheetId="29" r:id="rId28"/>
-    <sheet name="Sheet26" sheetId="30" r:id="rId29"/>
-    <sheet name="Sheet27" sheetId="31" r:id="rId30"/>
-    <sheet name="Sheet28" sheetId="32" r:id="rId31"/>
-    <sheet name="Sheet29" sheetId="33" r:id="rId32"/>
-    <sheet name="Sheet30" sheetId="34" r:id="rId33"/>
-    <sheet name="Sheet31" sheetId="35" r:id="rId34"/>
-    <sheet name="Sheet32" sheetId="36" r:id="rId35"/>
-    <sheet name="Sheet33" sheetId="37" r:id="rId36"/>
-    <sheet name="Sheet34" sheetId="38" r:id="rId37"/>
-    <sheet name="Sheet35" sheetId="39" r:id="rId38"/>
-    <sheet name="Sheet36" sheetId="40" r:id="rId39"/>
-    <sheet name="Sheet37" sheetId="41" r:id="rId40"/>
-    <sheet name="Sheet38" sheetId="42" r:id="rId41"/>
-    <sheet name="Sheet39" sheetId="43" r:id="rId42"/>
-    <sheet name="Sheet40" sheetId="44" r:id="rId43"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -2650,96 +2610,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E94464D4-EC1D-4FA0-AC40-66A467EC0964}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3AE0CA9-405C-4086-9C56-CE63580B449A}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15995D1D-FDF0-49C6-8ECD-4F5FC78221C7}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46922D0C-AA70-47C0-981A-967EE03D6C3C}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4D4A80C-4094-4F69-8614-637DB0E47D94}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62CFDE25-B95E-4367-88F9-4F9BFB49C1A6}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1B86F54-2294-49B8-ADD6-8EBAFCD85527}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53ECA507-449C-4C8A-A2AA-22A6B59F45D7}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89023118-6C73-4124-B7AA-225A3D06B710}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61575C6C-A079-42DD-B080-70791D352578}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0315EFF-635F-40C4-92EA-37C42B4E2E93}">
   <dimension ref="A1:D8"/>
@@ -2874,96 +2744,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51391442-8772-4747-A4BF-B475C7E33B1C}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2C0C972-BDE0-4FF5-9CBF-9CA51BBBEC53}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{224B232A-57F3-4811-86C9-FA17548A7E22}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28D69BCE-72F0-4D88-997B-5DB235E78B77}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C80B07B4-8CB3-415A-ABE2-3D5572F06803}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4FEC5A-A300-4B9A-A1C9-22BC0D6D8CB2}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ECD49C4-9D60-4B84-9C75-35D09029E2E6}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6367E4F9-1F1D-4D4C-A55B-2A720E92992F}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3745DC1-208B-48D0-AE15-C26A009618DC}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D51E4C66-F459-4454-AD60-333A1024BAB4}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEF9D56E-CE94-4D93-A8B5-535A0820AD51}">
   <dimension ref="A1:D15"/>
@@ -3194,184 +2974,4 @@
     </ext>
   </extLst>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FC1D91F-A606-4E23-BCC8-9DF35147A8FC}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3128FFCD-CB1D-4689-9AEA-B980E4E8AF28}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62335473-716F-41E1-B969-A29BAB24CE88}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B151F5B6-61D9-4E4D-A833-0A4E42510874}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C948862A-A018-4152-9AA1-E137DA89948C}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AE5714A-EE07-4ABB-B5B2-3ADBE3214464}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D358B63E-AC30-4B8E-AFA7-148098837145}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF1BFD0A-F4D1-48EB-A255-71E20A598CF1}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{663B8461-B94F-40E4-ABFF-F2A5B0C697EF}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF714D8E-0CDD-4814-8286-A3DBDC65584C}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA3FACD9-1807-42BF-B67D-498F268AAADA}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFABD89E-BB0B-4FD2-A11A-777F0F59CB49}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22005587-4C80-485E-B637-6D2394DE3CAE}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FBA76BF-0954-4E61-A150-B0A3899BA710}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40A39B4A-8FD5-4236-8396-62C97FF8DB07}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6019E687-BCD8-4FB3-9692-FA714D1CC31B}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E8BCAE6-FB71-4B36-9B23-91FA349B8AF1}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00CB4B69-3746-4982-A1F1-65B2ED3EFD11}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01DC096B-7A7C-40C0-9897-7CD7CA520658}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{616ED733-6DEB-463F-8060-428CB1F0EE76}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/data/team_stat.xlsx
+++ b/data/team_stat.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a225a4cd7e80232/Wasawat/Etheria/gvgplaner/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="289" documentId="11_625D4987526768CFEB3B98154B5DCE3A47CD54D3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8B1D5AA-F7A7-43C4-89E6-0AC8023A0E64}"/>
+  <xr:revisionPtr revIDLastSave="290" documentId="11_625D4987526768CFEB3B98154B5DCE3A47CD54D3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{98B8B102-01F9-4849-9692-252347C0BBAB}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Animus" sheetId="1" r:id="rId1"/>
-    <sheet name="W010" sheetId="4" r:id="rId2"/>
-    <sheet name="W011" sheetId="3" r:id="rId3"/>
+    <sheet name="W011" sheetId="3" r:id="rId2"/>
+    <sheet name="W010" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -2611,6 +2611,238 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEF9D56E-CE94-4D93-A8B5-535A0820AD51}">
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D4">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>78</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
+        <v>61</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>78</v>
+      </c>
+      <c r="B10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C10" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" t="s">
+        <v>76</v>
+      </c>
+      <c r="C11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>76</v>
+      </c>
+      <c r="B12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12" t="s">
+        <v>61</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>79</v>
+      </c>
+      <c r="B13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>57</v>
+      </c>
+      <c r="B14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" t="s">
+        <v>76</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{4EA8DDA0-AEBC-4499-84A7-672FAD55B1F3}">
+          <x14:formula1>
+            <xm:f>Animus!$A$2:$A$80</xm:f>
+          </x14:formula1>
+          <xm:sqref>A15 A2:C14 B15:C15</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0315EFF-635F-40C4-92EA-37C42B4E2E93}">
   <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2742,236 +2974,4 @@
     </ext>
   </extLst>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEF9D56E-CE94-4D93-A8B5-535A0820AD51}">
-  <dimension ref="A1:D15"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C1" t="s">
-        <v>83</v>
-      </c>
-      <c r="D1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>72</v>
-      </c>
-      <c r="B3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D4">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>70</v>
-      </c>
-      <c r="B5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B6" t="s">
-        <v>76</v>
-      </c>
-      <c r="C6" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>65</v>
-      </c>
-      <c r="B7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>65</v>
-      </c>
-      <c r="B8" t="s">
-        <v>53</v>
-      </c>
-      <c r="C8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>78</v>
-      </c>
-      <c r="B9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" t="s">
-        <v>61</v>
-      </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>78</v>
-      </c>
-      <c r="B10" t="s">
-        <v>73</v>
-      </c>
-      <c r="C10" t="s">
-        <v>33</v>
-      </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" t="s">
-        <v>76</v>
-      </c>
-      <c r="C11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>76</v>
-      </c>
-      <c r="B12" t="s">
-        <v>4</v>
-      </c>
-      <c r="C12" t="s">
-        <v>61</v>
-      </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>79</v>
-      </c>
-      <c r="B13" t="s">
-        <v>38</v>
-      </c>
-      <c r="C13" t="s">
-        <v>36</v>
-      </c>
-      <c r="D13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>57</v>
-      </c>
-      <c r="B14" t="s">
-        <v>19</v>
-      </c>
-      <c r="C14" t="s">
-        <v>37</v>
-      </c>
-      <c r="D14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>37</v>
-      </c>
-      <c r="B15" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" t="s">
-        <v>76</v>
-      </c>
-      <c r="D15">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{4EA8DDA0-AEBC-4499-84A7-672FAD55B1F3}">
-          <x14:formula1>
-            <xm:f>Animus!$A$2:$A$80</xm:f>
-          </x14:formula1>
-          <xm:sqref>A15 A2:C14 B15:C15</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
-</worksheet>
 </file>
--- a/data/team_stat.xlsx
+++ b/data/team_stat.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a225a4cd7e80232/Wasawat/Etheria/gvgplaner/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="290" documentId="11_625D4987526768CFEB3B98154B5DCE3A47CD54D3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{98B8B102-01F9-4849-9692-252347C0BBAB}"/>
+  <xr:revisionPtr revIDLastSave="291" documentId="11_625D4987526768CFEB3B98154B5DCE3A47CD54D3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D2DC878-863A-4235-90AF-A1C484E1ED18}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Animus" sheetId="1" r:id="rId1"/>
-    <sheet name="W011" sheetId="3" r:id="rId2"/>
-    <sheet name="W010" sheetId="4" r:id="rId3"/>
+    <sheet name="W010" sheetId="4" r:id="rId2"/>
+    <sheet name="W011" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -2611,6 +2611,140 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0315EFF-635F-40C4-92EA-37C42B4E2E93}">
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" t="s">
+        <v>79</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>68</v>
+      </c>
+      <c r="B8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{6537F7E5-878A-4B64-B8FC-8BEECBC5A566}">
+          <x14:formula1>
+            <xm:f>Animus!$A$2:$A$80</xm:f>
+          </x14:formula1>
+          <xm:sqref>A2:C8</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEF9D56E-CE94-4D93-A8B5-535A0820AD51}">
   <dimension ref="A1:D15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2840,138 +2974,4 @@
     </ext>
   </extLst>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0315EFF-635F-40C4-92EA-37C42B4E2E93}">
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C1" t="s">
-        <v>83</v>
-      </c>
-      <c r="D1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D4">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>70</v>
-      </c>
-      <c r="B5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" t="s">
-        <v>61</v>
-      </c>
-      <c r="C6" t="s">
-        <v>79</v>
-      </c>
-      <c r="D6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>57</v>
-      </c>
-      <c r="B7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>68</v>
-      </c>
-      <c r="B8" t="s">
-        <v>65</v>
-      </c>
-      <c r="C8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D8">
-        <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{6537F7E5-878A-4B64-B8FC-8BEECBC5A566}">
-          <x14:formula1>
-            <xm:f>Animus!$A$2:$A$80</xm:f>
-          </x14:formula1>
-          <xm:sqref>A2:C8</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
-</worksheet>
 </file>
--- a/data/team_stat.xlsx
+++ b/data/team_stat.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a225a4cd7e80232/Wasawat/Etheria/gvgplaner/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="291" documentId="11_625D4987526768CFEB3B98154B5DCE3A47CD54D3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D2DC878-863A-4235-90AF-A1C484E1ED18}"/>
+  <xr:revisionPtr revIDLastSave="293" documentId="11_625D4987526768CFEB3B98154B5DCE3A47CD54D3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A47637A3-9975-4277-BD09-FC3E1BCF314E}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10212" yWindow="1104" windowWidth="10320" windowHeight="10524" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Animus" sheetId="1" r:id="rId1"/>
-    <sheet name="W010" sheetId="4" r:id="rId2"/>
-    <sheet name="W011" sheetId="3" r:id="rId3"/>
+    <sheet name="W011" sheetId="4" r:id="rId2"/>
+    <sheet name="W012" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1213,10 +1213,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data/team_stat.xlsx
+++ b/data/team_stat.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a225a4cd7e80232/Wasawat/Etheria/gvgplaner/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="293" documentId="11_625D4987526768CFEB3B98154B5DCE3A47CD54D3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A47637A3-9975-4277-BD09-FC3E1BCF314E}"/>
+  <xr:revisionPtr revIDLastSave="374" documentId="11_625D4987526768CFEB3B98154B5DCE3A47CD54D3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F4663714-1FA4-4426-BD0C-D3469B704D20}"/>
   <bookViews>
-    <workbookView xWindow="10212" yWindow="1104" windowWidth="10320" windowHeight="10524" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Animus" sheetId="1" r:id="rId1"/>
     <sheet name="W011" sheetId="4" r:id="rId2"/>
     <sheet name="W012" sheetId="3" r:id="rId3"/>
+    <sheet name="W013" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -837,7 +838,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="85">
   <si>
     <t>Animus</t>
   </si>
@@ -1213,6 +1214,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2970,4 +2975,250 @@
     </ext>
   </extLst>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF4E6699-D53D-4620-B249-D57B2C33655D}">
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" t="s">
+        <v>79</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" t="s">
+        <v>70</v>
+      </c>
+      <c r="D7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" t="s">
+        <v>68</v>
+      </c>
+      <c r="D8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>79</v>
+      </c>
+      <c r="B9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" t="s">
+        <v>65</v>
+      </c>
+      <c r="D10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" t="s">
+        <v>57</v>
+      </c>
+      <c r="C11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B12" t="s">
+        <v>78</v>
+      </c>
+      <c r="C12" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" t="s">
+        <v>46</v>
+      </c>
+      <c r="C13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14" t="s">
+        <v>65</v>
+      </c>
+      <c r="D14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>65</v>
+      </c>
+      <c r="B15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" t="s">
+        <v>37</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{5131E174-52DD-43B0-89F4-142D3F29FB8E}">
+          <x14:formula1>
+            <xm:f>Animus!$A$2:$A$80</xm:f>
+          </x14:formula1>
+          <xm:sqref>A2:C15</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
 </file>
--- a/data/team_stat.xlsx
+++ b/data/team_stat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a225a4cd7e80232/Wasawat/Etheria/gvgplaner/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="374" documentId="11_625D4987526768CFEB3B98154B5DCE3A47CD54D3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F4663714-1FA4-4426-BD0C-D3469B704D20}"/>
+  <xr:revisionPtr revIDLastSave="414" documentId="11_625D4987526768CFEB3B98154B5DCE3A47CD54D3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB4FD597-0639-43CB-A32E-BE14D036358C}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2979,8 +2979,13 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF4E6699-D53D-4620-B249-D57B2C33655D}">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.44140625" customWidth="1"/>
+    <col min="2" max="2" width="10.6640625" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -3054,7 +3059,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="B6" t="s">
         <v>3</v>
@@ -3063,7 +3068,7 @@
         <v>65</v>
       </c>
       <c r="D6">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -3091,7 +3096,7 @@
         <v>68</v>
       </c>
       <c r="D8">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -3116,52 +3121,52 @@
         <v>57</v>
       </c>
       <c r="C10" t="s">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="D10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="B11" t="s">
         <v>57</v>
       </c>
       <c r="C11" t="s">
-        <v>19</v>
+        <v>65</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="B12" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="C12" t="s">
-        <v>68</v>
+        <v>19</v>
       </c>
       <c r="D12">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>3</v>
+        <v>65</v>
       </c>
       <c r="B13" t="s">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="C13" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="D13">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -3172,10 +3177,10 @@
         <v>46</v>
       </c>
       <c r="C14" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="D14">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -3204,6 +3209,12 @@
       </c>
       <c r="D16">
         <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D17">
+        <f>SUM(D2:D16)</f>
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/data/team_stat.xlsx
+++ b/data/team_stat.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a225a4cd7e80232/Wasawat/Etheria/gvgplaner/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="414" documentId="11_625D4987526768CFEB3B98154B5DCE3A47CD54D3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB4FD597-0639-43CB-A32E-BE14D036358C}"/>
+  <xr:revisionPtr revIDLastSave="580" documentId="11_625D4987526768CFEB3B98154B5DCE3A47CD54D3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4B86339-DE6E-45BC-A5DB-9C74F9765D62}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="492" yWindow="2676" windowWidth="10488" windowHeight="9144" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Animus" sheetId="1" r:id="rId1"/>
     <sheet name="W011" sheetId="4" r:id="rId2"/>
     <sheet name="W012" sheetId="3" r:id="rId3"/>
     <sheet name="W013" sheetId="5" r:id="rId4"/>
+    <sheet name="W014" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="79">
+  <futureMetadata name="XLRICHVALUE" count="80">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -594,8 +595,15 @@
         </ext>
       </extLst>
     </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="79"/>
+        </ext>
+      </extLst>
+    </bk>
   </futureMetadata>
-  <valueMetadata count="79">
+  <valueMetadata count="80">
     <bk>
       <rc t="1" v="0"/>
     </bk>
@@ -832,13 +840,16 @@
     </bk>
     <bk>
       <rc t="1" v="78"/>
+    </bk>
+    <bk>
+      <rc t="1" v="79"/>
     </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="86">
   <si>
     <t>Animus</t>
   </si>
@@ -1093,6 +1104,9 @@
   </si>
   <si>
     <t>DEF_Win</t>
+  </si>
+  <si>
+    <t>Jolt</t>
   </si>
 </sst>
 </file>
@@ -1175,7 +1189,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1198,6 +1212,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1261,7 +1278,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="79">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="80">
   <rv s="0">
     <v>0</v>
     <v>5</v>
@@ -1576,6 +1593,10 @@
   </rv>
   <rv s="0">
     <v>78</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>79</v>
     <v>5</v>
   </rv>
 </rvData>
@@ -1671,6 +1692,7 @@
   <rel r:id="rId77"/>
   <rel r:id="rId78"/>
   <rel r:id="rId79"/>
+  <rel r:id="rId80"/>
 </richValueRels>
 </file>
 
@@ -1959,7 +1981,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B80"/>
+  <dimension ref="A1:B81"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -2183,24 +2205,24 @@
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" s="6" t="s">
+      <c r="A28" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B28" s="9" t="e" vm="27">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B28" s="7" t="e" vm="27">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B29" s="2" t="e" vm="28">
+      <c r="B29" s="7" t="e" vm="28">
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B30" s="2" t="e" vm="29">
         <v>#VALUE!</v>
@@ -2208,7 +2230,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B31" s="2" t="e" vm="30">
         <v>#VALUE!</v>
@@ -2216,7 +2238,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B32" s="2" t="e" vm="31">
         <v>#VALUE!</v>
@@ -2224,7 +2246,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B33" s="2" t="e" vm="32">
         <v>#VALUE!</v>
@@ -2232,7 +2254,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B34" s="2" t="e" vm="33">
         <v>#VALUE!</v>
@@ -2240,7 +2262,7 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B35" s="2" t="e" vm="34">
         <v>#VALUE!</v>
@@ -2248,7 +2270,7 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B36" s="2" t="e" vm="35">
         <v>#VALUE!</v>
@@ -2256,7 +2278,7 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B37" s="2" t="e" vm="36">
         <v>#VALUE!</v>
@@ -2264,7 +2286,7 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B38" s="2" t="e" vm="37">
         <v>#VALUE!</v>
@@ -2272,7 +2294,7 @@
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B39" s="2" t="e" vm="38">
         <v>#VALUE!</v>
@@ -2280,7 +2302,7 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B40" s="2" t="e" vm="39">
         <v>#VALUE!</v>
@@ -2288,7 +2310,7 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B41" s="2" t="e" vm="40">
         <v>#VALUE!</v>
@@ -2296,7 +2318,7 @@
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B42" s="2" t="e" vm="41">
         <v>#VALUE!</v>
@@ -2304,7 +2326,7 @@
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B43" s="2" t="e" vm="42">
         <v>#VALUE!</v>
@@ -2312,7 +2334,7 @@
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B44" s="2" t="e" vm="43">
         <v>#VALUE!</v>
@@ -2320,23 +2342,23 @@
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B45" s="2" t="e" vm="44">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B45" s="2" t="e" vm="44">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A46" s="4" t="s">
+      <c r="B46" s="2" t="e" vm="45">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" s="4" t="s">
         <v>46</v>
-      </c>
-      <c r="B46" s="2" t="e" vm="45">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A47" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="B47" s="2" t="e" vm="46">
         <v>#VALUE!</v>
@@ -2344,7 +2366,7 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B48" s="2" t="e" vm="47">
         <v>#VALUE!</v>
@@ -2352,7 +2374,7 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B49" s="2" t="e" vm="48">
         <v>#VALUE!</v>
@@ -2360,7 +2382,7 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B50" s="2" t="e" vm="49">
         <v>#VALUE!</v>
@@ -2368,31 +2390,31 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B51" s="8" t="e" vm="50">
+        <v>50</v>
+      </c>
+      <c r="B51" s="2" t="e" vm="50">
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B52" s="8" t="e" vm="51">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B52" s="2" t="e" vm="51">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A53" s="4" t="s">
+      <c r="B53" s="2" t="e" vm="52">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A54" s="4" t="s">
         <v>53</v>
-      </c>
-      <c r="B53" s="2" t="e" vm="52">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A54" s="3" t="s">
-        <v>54</v>
       </c>
       <c r="B54" s="2" t="e" vm="53">
         <v>#VALUE!</v>
@@ -2400,7 +2422,7 @@
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B55" s="2" t="e" vm="54">
         <v>#VALUE!</v>
@@ -2408,7 +2430,7 @@
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B56" s="2" t="e" vm="55">
         <v>#VALUE!</v>
@@ -2416,7 +2438,7 @@
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B57" s="2" t="e" vm="56">
         <v>#VALUE!</v>
@@ -2424,7 +2446,7 @@
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B58" s="2" t="e" vm="57">
         <v>#VALUE!</v>
@@ -2432,7 +2454,7 @@
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B59" s="2" t="e" vm="58">
         <v>#VALUE!</v>
@@ -2440,7 +2462,7 @@
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B60" s="2" t="e" vm="59">
         <v>#VALUE!</v>
@@ -2448,7 +2470,7 @@
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B61" s="2" t="e" vm="60">
         <v>#VALUE!</v>
@@ -2456,7 +2478,7 @@
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B62" s="2" t="e" vm="61">
         <v>#VALUE!</v>
@@ -2464,7 +2486,7 @@
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B63" s="2" t="e" vm="62">
         <v>#VALUE!</v>
@@ -2472,7 +2494,7 @@
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B64" s="2" t="e" vm="63">
         <v>#VALUE!</v>
@@ -2480,7 +2502,7 @@
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B65" s="2" t="e" vm="64">
         <v>#VALUE!</v>
@@ -2488,7 +2510,7 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B66" s="2" t="e" vm="65">
         <v>#VALUE!</v>
@@ -2496,23 +2518,23 @@
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B67" s="2" t="e" vm="66">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A68" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B67" s="2" t="e" vm="66">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A68" s="4" t="s">
+      <c r="B68" s="2" t="e" vm="67">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A69" s="4" t="s">
         <v>68</v>
-      </c>
-      <c r="B68" s="2" t="e" vm="67">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A69" s="3" t="s">
-        <v>69</v>
       </c>
       <c r="B69" s="2" t="e" vm="68">
         <v>#VALUE!</v>
@@ -2520,7 +2542,7 @@
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B70" s="2" t="e" vm="69">
         <v>#VALUE!</v>
@@ -2528,7 +2550,7 @@
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B71" s="2" t="e" vm="70">
         <v>#VALUE!</v>
@@ -2536,7 +2558,7 @@
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B72" s="2" t="e" vm="71">
         <v>#VALUE!</v>
@@ -2544,7 +2566,7 @@
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B73" s="2" t="e" vm="72">
         <v>#VALUE!</v>
@@ -2552,7 +2574,7 @@
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B74" s="2" t="e" vm="73">
         <v>#VALUE!</v>
@@ -2560,7 +2582,7 @@
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B75" s="2" t="e" vm="74">
         <v>#VALUE!</v>
@@ -2568,7 +2590,7 @@
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B76" s="2" t="e" vm="75">
         <v>#VALUE!</v>
@@ -2576,23 +2598,23 @@
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="B77" s="5" t="e" vm="76">
+        <v>76</v>
+      </c>
+      <c r="B77" s="2" t="e" vm="76">
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B78" s="2" t="e" vm="77">
+        <v>77</v>
+      </c>
+      <c r="B78" s="5" t="e" vm="77">
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B79" s="2" t="e" vm="78">
         <v>#VALUE!</v>
@@ -2600,9 +2622,17 @@
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B80" s="2" t="e" vm="79">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B80" s="2" t="e" vm="79">
+      <c r="B81" s="2" t="e" vm="80">
         <v>#VALUE!</v>
       </c>
     </row>
@@ -2735,7 +2765,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{6537F7E5-878A-4B64-B8FC-8BEECBC5A566}">
           <x14:formula1>
-            <xm:f>Animus!$A$2:$A$80</xm:f>
+            <xm:f>Animus!$A$2:$A$81</xm:f>
           </x14:formula1>
           <xm:sqref>A2:C8</xm:sqref>
         </x14:dataValidation>
@@ -2967,9 +2997,9 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{4EA8DDA0-AEBC-4499-84A7-672FAD55B1F3}">
           <x14:formula1>
-            <xm:f>Animus!$A$2:$A$80</xm:f>
+            <xm:f>Animus!$A$2:$A$81</xm:f>
           </x14:formula1>
-          <xm:sqref>A15 A2:C14 B15:C15</xm:sqref>
+          <xm:sqref>A2:C15</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2979,7 +3009,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF4E6699-D53D-4620-B249-D57B2C33655D}">
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.44140625" customWidth="1"/>
@@ -3211,12 +3241,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D17">
-        <f>SUM(D2:D16)</f>
-        <v>50</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
@@ -3224,7 +3248,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{5131E174-52DD-43B0-89F4-142D3F29FB8E}">
           <x14:formula1>
-            <xm:f>Animus!$A$2:$A$80</xm:f>
+            <xm:f>Animus!$A$2:$A$81</xm:f>
           </x14:formula1>
           <xm:sqref>A2:C15</xm:sqref>
         </x14:dataValidation>
@@ -3232,4 +3256,466 @@
     </ext>
   </extLst>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54AF841C-518C-4293-8600-E43625BC0289}">
+  <dimension ref="A1:D31"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.5546875" customWidth="1"/>
+    <col min="2" max="2" width="10.88671875" customWidth="1"/>
+    <col min="3" max="3" width="11.5546875" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>78</v>
+      </c>
+      <c r="B8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>76</v>
+      </c>
+      <c r="B10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>78</v>
+      </c>
+      <c r="B11" t="s">
+        <v>73</v>
+      </c>
+      <c r="C11" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>57</v>
+      </c>
+      <c r="B12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>46</v>
+      </c>
+      <c r="B13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" t="s">
+        <v>68</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>57</v>
+      </c>
+      <c r="B14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" t="s">
+        <v>65</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" t="s">
+        <v>70</v>
+      </c>
+      <c r="D15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>65</v>
+      </c>
+      <c r="B16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" t="s">
+        <v>57</v>
+      </c>
+      <c r="D16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17" t="s">
+        <v>68</v>
+      </c>
+      <c r="C17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>73</v>
+      </c>
+      <c r="B18" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" t="s">
+        <v>76</v>
+      </c>
+      <c r="D18">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B19" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" t="s">
+        <v>65</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>68</v>
+      </c>
+      <c r="B20" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" t="s">
+        <v>37</v>
+      </c>
+      <c r="D20">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B21" t="s">
+        <v>68</v>
+      </c>
+      <c r="C21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>46</v>
+      </c>
+      <c r="B22" t="s">
+        <v>3</v>
+      </c>
+      <c r="C22" t="s">
+        <v>73</v>
+      </c>
+      <c r="D22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>68</v>
+      </c>
+      <c r="B23" t="s">
+        <v>53</v>
+      </c>
+      <c r="C23" t="s">
+        <v>37</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24" t="s">
+        <v>3</v>
+      </c>
+      <c r="C24" t="s">
+        <v>19</v>
+      </c>
+      <c r="D24">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>46</v>
+      </c>
+      <c r="B25" t="s">
+        <v>3</v>
+      </c>
+      <c r="C25" t="s">
+        <v>37</v>
+      </c>
+      <c r="D25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>57</v>
+      </c>
+      <c r="B26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C26" t="s">
+        <v>61</v>
+      </c>
+      <c r="D26">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>3</v>
+      </c>
+      <c r="B27" t="s">
+        <v>37</v>
+      </c>
+      <c r="C27" t="s">
+        <v>70</v>
+      </c>
+      <c r="D27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>46</v>
+      </c>
+      <c r="B28" t="s">
+        <v>29</v>
+      </c>
+      <c r="C28" t="s">
+        <v>68</v>
+      </c>
+      <c r="D28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>65</v>
+      </c>
+      <c r="B29" t="s">
+        <v>57</v>
+      </c>
+      <c r="C29" t="s">
+        <v>19</v>
+      </c>
+      <c r="D29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>3</v>
+      </c>
+      <c r="B30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C30" t="s">
+        <v>70</v>
+      </c>
+      <c r="D30">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>57</v>
+      </c>
+      <c r="B31" t="s">
+        <v>19</v>
+      </c>
+      <c r="C31" t="s">
+        <v>37</v>
+      </c>
+      <c r="D31">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E945C850-C0B1-427E-9545-A28333148AF7}">
+          <x14:formula1>
+            <xm:f>Animus!$A$2:$A$81</xm:f>
+          </x14:formula1>
+          <xm:sqref>A2:C31</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
 </file>
--- a/data/team_stat.xlsx
+++ b/data/team_stat.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a225a4cd7e80232/Wasawat/Etheria/gvgplaner/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="580" documentId="11_625D4987526768CFEB3B98154B5DCE3A47CD54D3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4B86339-DE6E-45BC-A5DB-9C74F9765D62}"/>
+  <xr:revisionPtr revIDLastSave="694" documentId="11_625D4987526768CFEB3B98154B5DCE3A47CD54D3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A9E6CD15-4056-45EB-A8FC-2F7472221DD1}"/>
   <bookViews>
-    <workbookView xWindow="492" yWindow="2676" windowWidth="10488" windowHeight="9144" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Animus" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="W012" sheetId="3" r:id="rId3"/>
     <sheet name="W013" sheetId="5" r:id="rId4"/>
     <sheet name="W014" sheetId="6" r:id="rId5"/>
+    <sheet name="W015" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -849,7 +850,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="86">
   <si>
     <t>Animus</t>
   </si>
@@ -3718,4 +3719,421 @@
     </ext>
   </extLst>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{400E8CBF-D2E3-4F08-A0CB-82523B7015CE}">
+  <dimension ref="A1:D28"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" t="s">
+        <v>76</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" t="s">
+        <v>70</v>
+      </c>
+      <c r="D8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
+        <v>79</v>
+      </c>
+      <c r="C10" t="s">
+        <v>78</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11" t="s">
+        <v>65</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>78</v>
+      </c>
+      <c r="B12" t="s">
+        <v>85</v>
+      </c>
+      <c r="C12" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>57</v>
+      </c>
+      <c r="B13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" t="s">
+        <v>57</v>
+      </c>
+      <c r="C14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" t="s">
+        <v>65</v>
+      </c>
+      <c r="C15" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>68</v>
+      </c>
+      <c r="B16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" t="s">
+        <v>29</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" t="s">
+        <v>65</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>78</v>
+      </c>
+      <c r="B18" t="s">
+        <v>3</v>
+      </c>
+      <c r="C18" t="s">
+        <v>37</v>
+      </c>
+      <c r="D18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>65</v>
+      </c>
+      <c r="B19" t="s">
+        <v>70</v>
+      </c>
+      <c r="C19" t="s">
+        <v>48</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>57</v>
+      </c>
+      <c r="B20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" t="s">
+        <v>65</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B21" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" t="s">
+        <v>70</v>
+      </c>
+      <c r="D21">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" t="s">
+        <v>78</v>
+      </c>
+      <c r="C22" t="s">
+        <v>73</v>
+      </c>
+      <c r="D22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" t="s">
+        <v>70</v>
+      </c>
+      <c r="C23" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>46</v>
+      </c>
+      <c r="B24" t="s">
+        <v>68</v>
+      </c>
+      <c r="C24" t="s">
+        <v>29</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>19</v>
+      </c>
+      <c r="B25" t="s">
+        <v>65</v>
+      </c>
+      <c r="C25" t="s">
+        <v>57</v>
+      </c>
+      <c r="D25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>78</v>
+      </c>
+      <c r="B26" t="s">
+        <v>73</v>
+      </c>
+      <c r="C26" t="s">
+        <v>33</v>
+      </c>
+      <c r="D26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>46</v>
+      </c>
+      <c r="B27" t="s">
+        <v>29</v>
+      </c>
+      <c r="C27" t="s">
+        <v>17</v>
+      </c>
+      <c r="D27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>68</v>
+      </c>
+      <c r="B28" t="s">
+        <v>53</v>
+      </c>
+      <c r="C28" t="s">
+        <v>79</v>
+      </c>
+      <c r="D28">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{0D7EB8B6-0B11-4BA3-85DA-28DB9086D453}">
+          <x14:formula1>
+            <xm:f>Animus!$A$2:$A$81</xm:f>
+          </x14:formula1>
+          <xm:sqref>A2:C28</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
 </file>